--- a/plantillas/91.xlsx
+++ b/plantillas/91.xlsx
@@ -45,7 +45,7 @@
     <definedName name="MARCA_31">Listas!$AH$2:$AH$6</definedName>
     <definedName name="MARCA_32">Listas!$AI$2:$AI$2</definedName>
     <definedName name="MARCA_33">Listas!$AJ$2:$AJ$2</definedName>
-    <definedName name="MARCA_34">Listas!$AK$2:$AK$19</definedName>
+    <definedName name="MARCA_34">Listas!$AK$2:$AK$18</definedName>
     <definedName name="MARCA_35">Listas!$AL$2:$AL$28</definedName>
     <definedName name="MARCA_36">Listas!$AM$2:$AM$68</definedName>
     <definedName name="MARCA_37">Listas!$AN$2:$AN$36</definedName>
@@ -53,7 +53,7 @@
     <definedName name="MARCA_39">Listas!$AP$2:$AP$14</definedName>
     <definedName name="MARCA_40">Listas!$AQ$2:$AQ$2</definedName>
     <definedName name="MARCA_41">Listas!$AR$2:$AR$27</definedName>
-    <definedName name="MARCA_42">Listas!$AS$2:$AS$25</definedName>
+    <definedName name="MARCA_42">Listas!$AS$2:$AS$24</definedName>
     <definedName name="MARCA_43">Listas!$AT$2:$AT$7</definedName>
     <definedName name="MARCA_44">Listas!$AU$2:$AU$51</definedName>
     <definedName name="MARCA_45">Listas!$AV$2:$AV$9</definedName>
@@ -67,7 +67,7 @@
     <definedName name="MARCA_53">Listas!$BD$2:$BD$7</definedName>
     <definedName name="MARCA_54">Listas!$BE$2:$BE$11</definedName>
     <definedName name="MARCA_55">Listas!$BF$2:$BF$2</definedName>
-    <definedName name="MARCA_56">Listas!$BG$2:$BG$19</definedName>
+    <definedName name="MARCA_56">Listas!$BG$2:$BG$21</definedName>
     <definedName name="MARCA_57">Listas!$BH$2:$BH$18</definedName>
     <definedName name="MARCA_58">Listas!$BI$2:$BI$3</definedName>
     <definedName name="MARCA_59">Listas!$BJ$2:$BJ$6</definedName>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
+          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11630,11 +11630,6 @@
           <t>KT ALIMENTO PARA KOI 3LB · 93500000266</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
-        </is>
-      </c>
       <c r="AL19" t="inlineStr">
         <is>
           <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
@@ -11657,7 +11652,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SD PD CANINE METABOLISMO 7LB · 93517000000</t>
+          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -11672,7 +11667,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>TOW VALLE DE APALACHES V. Y GARB 5.6KG · 90013220000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -11739,7 +11734,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
+          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -11750,6 +11745,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>ROYAL CANIN HEPATIC 7KG · 90021670000</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
         </is>
       </c>
       <c r="BK20" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
+          <t>SD PD GATO I/D 4LB · 93517090000</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -11827,6 +11827,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>TOW VALLE DE APALACHES V. Y GARB 5.6KG · 90013220000</t>
         </is>
       </c>
       <c r="BK21" t="inlineStr">
@@ -11893,7 +11898,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D 4LB · 93517090000</t>
+          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -11965,7 +11970,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
+          <t>SD PD GATOS W/D 4LB · 93517050000</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -12037,7 +12042,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SD PD GATOS W/D 4LB · 93517050000</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -12105,11 +12110,6 @@
       <c r="AR25" t="inlineStr">
         <is>
           <t>PF ROLLO/CARNAZA SABOR NATURAL 10IN · 93517740000</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -20998,12 +20998,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>D NV ELECTROLITOS P/ PERROS/GATOS 16 · 90328660000</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90328660000</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -21011,23 +21011,23 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>D NV ELECTROLITOS P/ PERROS/GATOS 16 · 90328660000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>90328660000</t>
+          <t>90328330000</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -21038,16 +21038,16 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>90328330000</t>
+          <t>93518700000</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -21058,16 +21058,16 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
+          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>93518700000</t>
+          <t>90328760000</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -21078,12 +21078,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
+          <t>D NV TABLETAS CON ARANDANOS P/VEJIGA · 90327400000</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>90328760000</t>
+          <t>90327400000</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -21098,16 +21098,16 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>D NV TABLETAS CON ARANDANOS P/VEJIGA · 90327400000</t>
+          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>90327400000</t>
+          <t>90328340000</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -21118,16 +21118,16 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
+          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>90328340000</t>
+          <t>90327410000</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -21138,16 +21138,16 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
+          <t>NUTV GALLETAS M MANI ARTICULACIONES · 90022430000</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>90327410000</t>
+          <t>90022430000</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -21158,12 +21158,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>NUTV GALLETAS M MANI ARTICULACIONES · 90022430000</t>
+          <t>NUTV GALLETAS PARA SOP. PIEL Y PELAJE · 90022390000</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>90022430000</t>
+          <t>90022390000</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -21178,12 +21178,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>NUTV GALLETAS PARA SOP. PIEL Y PELAJE · 90022390000</t>
+          <t>NUTV GALLETAS PARA SOP.SIST INMUNE · 90022410000</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>90022390000</t>
+          <t>90022410000</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -21198,12 +21198,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>NUTV GALLETAS PARA SOP.SIST INMUNE · 90022410000</t>
+          <t>NUTV GATOS SUP GEL SABOR POLLO 3OZ · 90022540000</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>90022410000</t>
+          <t>90022540000</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -21218,12 +21218,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>NUTV GATOS SUP GEL SABOR POLLO 3OZ · 90022540000</t>
+          <t>NUTV GATOS SUP GEL SABOR SALMON 3 OZ · 90022550000</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>90022540000</t>
+          <t>90022550000</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -21238,12 +21238,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>NUTV GATOS SUP GEL SABOR SALMON 3 OZ · 90022550000</t>
+          <t>NUTV SUP EN GEL P ARTICULACIONES 3OZ · 90022530000</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>90022550000</t>
+          <t>90022530000</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -21258,12 +21258,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>NUTV SUP EN GEL P ARTICULACIONES 3OZ · 90022530000</t>
+          <t>NUTV SUPL VITAMINICO GEL P GATOS 3OZ · 90022570000</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>90022530000</t>
+          <t>90022570000</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -21278,16 +21278,16 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>NUTV SUPL VITAMINICO GEL P GATOS 3OZ · 90022570000</t>
+          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>90022570000</t>
+          <t>90327670000</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -21298,16 +21298,16 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>90327670000</t>
+          <t>90327780000</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -21318,16 +21318,16 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>90327780000</t>
+          <t>90328050000</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -21338,16 +21338,16 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
+          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>90328050000</t>
+          <t>90328310000</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -21358,16 +21358,16 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
+          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>90328310000</t>
+          <t>90327630000</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -21378,16 +21378,16 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
+          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>90327630000</t>
+          <t>90327640000</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -21398,16 +21398,16 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
+          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>90327640000</t>
+          <t>90328780000</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -21418,16 +21418,16 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
+          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>90328780000</t>
+          <t>90328700000</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -21438,12 +21438,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
+          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>90328700000</t>
+          <t>90328770000</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -21458,16 +21458,16 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
+          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>90328770000</t>
+          <t>90328860000</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -21478,16 +21478,16 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
+          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>90328860000</t>
+          <t>90328840000</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -21498,16 +21498,16 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
+          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>90328840000</t>
+          <t>90327290000</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -21518,16 +21518,16 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
+          <t>NV VITAMINAS PERROS/GATOS 200UD · 90328320000</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>90327290000</t>
+          <t>90328320000</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -21538,36 +21538,36 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>NV VITAMINAS PERROS/GATOS 200UD · 90328320000</t>
+          <t>D NS GATO SENIOR CTRL PESO POLLO 4LB · 93500000485</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>90328320000</t>
+          <t>93500000485</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>D NS GATO SENIOR CTRL PESO POLLO 4LB · 93500000485</t>
+          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>93500000485</t>
+          <t>93500000457</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -21578,16 +21578,16 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
+          <t>NS CACHORRO RZ GDE GF 4LB · 93500000458</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>93500000457</t>
+          <t>93500000458</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -21598,16 +21598,16 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE GF 4LB · 93500000458</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 12LB · 93500000428</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>93500000458</t>
+          <t>93500000428</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -21618,16 +21618,16 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 12LB · 93500000428</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>93500000428</t>
+          <t>93500000429</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -21638,16 +21638,16 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>93500000429</t>
+          <t>93500000460</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -21658,16 +21658,16 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>93500000460</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -21678,16 +21678,16 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000425</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -21698,16 +21698,16 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
+          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>93500000425</t>
+          <t>93500000426</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -21718,16 +21718,16 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>93500000426</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -21738,16 +21738,16 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -21758,16 +21758,16 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -21778,12 +21778,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -21798,16 +21798,16 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -21818,16 +21818,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -21838,16 +21838,16 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -21858,16 +21858,16 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034150000</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -21878,16 +21878,16 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>90034150000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -21898,16 +21898,16 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -21918,16 +21918,16 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE R GDE CARNE Y CEBADA 40LB · 90034030000</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034030000</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -21938,16 +21938,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>NS CHOICE R GDE CARNE Y CEBADA 40LB · 90034030000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>90034030000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -21958,12 +21958,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -21978,12 +21978,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -21998,16 +21998,16 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>93500000416</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -22018,16 +22018,16 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
+          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>93500000416</t>
+          <t>93500000479</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -22038,16 +22038,16 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
+          <t>NS GATO Y GATITO POLLO Y ARROZ 4LB · 93500000477</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>93500000479</t>
+          <t>93500000477</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -22058,16 +22058,16 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO Y ARROZ 4LB · 93500000477</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>93500000477</t>
+          <t>93500000469</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -22078,16 +22078,16 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>93500000469</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000488</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -22118,16 +22118,16 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>93500000488</t>
+          <t>93500000486</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -22138,16 +22138,16 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>93500000486</t>
+          <t>93500000487</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>93500000487</t>
+          <t>93500000475</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -22178,16 +22178,16 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>93500000475</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -22198,16 +22198,16 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>93500000468</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -22218,16 +22218,16 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>93500000468</t>
+          <t>93500000467</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -22238,16 +22238,16 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>93500000467</t>
+          <t>93500000473</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -22258,16 +22258,16 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>93500000473</t>
+          <t>93500000466</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -22278,16 +22278,16 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS LATA SENIOR POLLO 13OZ · 93500000470</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>93500000466</t>
+          <t>93500000470</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -22298,16 +22298,16 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>NS LATA SENIOR POLLO 13OZ · 93500000470</t>
+          <t>NS PERFORMANCE PERRO POLLO ARROZ 40LB · 93500000415</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>93500000470</t>
+          <t>93500000415</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -22318,16 +22318,16 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>NS PERFORMANCE PERRO POLLO ARROZ 40LB · 93500000415</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>93500000415</t>
+          <t>93500000419</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -22338,16 +22338,16 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>93500000419</t>
+          <t>93500000420</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -22358,12 +22358,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
+          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>93500000420</t>
+          <t>93500000423</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -22378,12 +22378,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 12LB · 93500000421</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>93500000423</t>
+          <t>93500000421</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -22398,16 +22398,16 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 12LB · 93500000421</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>93500000421</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -22418,16 +22418,16 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>93500000422</t>
+          <t>93500000434</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -22438,16 +22438,16 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
+          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>93500000434</t>
+          <t>93500000436</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -22458,16 +22458,16 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>93500000436</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -22478,16 +22478,16 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000451</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -22498,16 +22498,16 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>93500000451</t>
+          <t>93500000452</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -22518,16 +22518,16 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 12LB · 93500000444</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>93500000452</t>
+          <t>93500000444</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -22538,16 +22538,16 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 12LB · 93500000444</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>93500000444</t>
+          <t>93500000445</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -22558,16 +22558,16 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>93500000445</t>
+          <t>93500000463</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -22578,16 +22578,16 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>93500000463</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -22598,16 +22598,16 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000441</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -22618,16 +22618,16 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>93500000441</t>
+          <t>93500000442</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -22638,16 +22638,16 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>93500000442</t>
+          <t>93500000449</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -22658,16 +22658,16 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>93500000449</t>
+          <t>93500000450</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -22678,16 +22678,16 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>93500000450</t>
+          <t>93500000438</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -22698,16 +22698,16 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>93500000438</t>
+          <t>93500000439</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -22718,16 +22718,16 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
+          <t>NS PERRO RZ GDE POLLO Y ARROZ 26LB · 93500000424</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>93500000439</t>
+          <t>93500000424</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -22738,16 +22738,16 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>NS PERRO RZ GDE POLLO Y ARROZ 26LB · 93500000424</t>
+          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>93500000424</t>
+          <t>93500000454</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -22758,16 +22758,16 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
+          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>93500000454</t>
+          <t>93500000455</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -22778,12 +22778,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
+          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>93500000455</t>
+          <t>93500000431</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -22798,16 +22798,16 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
+          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>93500000431</t>
+          <t>93500000432</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -22818,16 +22818,16 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
+          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>93500000432</t>
+          <t>93500000495</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -22838,16 +22838,16 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
+          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>93500000495</t>
+          <t>93500000496</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -22858,16 +22858,16 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
+          <t>NS SNACK GF PEQ BOCADOS CARNE 6OZ · 93500000494</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>93500000496</t>
+          <t>93500000494</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -22878,12 +22878,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>NS SNACK GF PEQ BOCADOS CARNE 6OZ · 93500000494</t>
+          <t>D NY SNACK DENTAL FILET MIGNON MINI78 · 93513790000</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>93500000494</t>
+          <t>93513790000</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -22891,23 +22891,23 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>D NY SNACK DENTAL FILET MIGNON MINI78 · 93513790000</t>
+          <t>D NYLABONE HUESO REG CARNE ASADA · 93508290000</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>93513790000</t>
+          <t>93508290000</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -22918,16 +22918,16 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO REG CARNE ASADA · 93508290000</t>
+          <t>D NYLABONE HUESO REG PAVO/MANZANA · 93508110000</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>93508290000</t>
+          <t>93508110000</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -22938,16 +22938,16 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO REG PAVO/MANZANA · 93508110000</t>
+          <t>D NYLABONE HUESO WOLF SABOR TOCINO · 93508210000</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>93508110000</t>
+          <t>93508210000</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -22958,16 +22958,16 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>D NYLABONE HUESO WOLF SABOR TOCINO · 93508210000</t>
+          <t>M MENUDEO NY SNACKS MINI 9350441 · 93515550000</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>93508210000</t>
+          <t>93515550000</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -22978,16 +22978,16 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>M MENUDEO NY SNACKS MINI 9350441 · 93515550000</t>
+          <t>NUBZ CALDO CON SABOR JAMÓN 1UD GIGANTE · 90022080000</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>93515550000</t>
+          <t>90022080000</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -22998,12 +22998,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>NUBZ CALDO CON SABOR JAMÓN 1UD GIGANTE · 90022080000</t>
+          <t>NUBZ CARNE DE RES CON RELLENO 16UD PQNO · 90022120000</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>90022080000</t>
+          <t>90022120000</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -23018,16 +23018,16 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>NUBZ CARNE DE RES CON RELLENO 16UD PQNO · 90022120000</t>
+          <t>NUBZ CARNE DE RES CON RELLENO 2UD GRD · 90022110000</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>90022120000</t>
+          <t>90022110000</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -23038,12 +23038,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>NUBZ CARNE DE RES CON RELLENO 2UD GRD · 90022110000</t>
+          <t>NUBZ MANTEQUILLA DE MANI 2UD GRANDE · 90022060000</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>90022110000</t>
+          <t>90022060000</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -23058,16 +23058,16 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>NUBZ MANTEQUILLA DE MANI 2UD GRANDE · 90022060000</t>
+          <t>NUBZ PAVO Y BATATA P CACHORRO 8UD PQNO · 90022140000</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>90022060000</t>
+          <t>90022140000</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -23078,16 +23078,16 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>NUBZ PAVO Y BATATA P CACHORRO 8UD PQNO · 90022140000</t>
+          <t>NUBZ SABOR CARNE 1UD EXTRA GRANDE · 90022050000</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>90022140000</t>
+          <t>90022050000</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -23098,12 +23098,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>NUBZ SABOR CARNE 1UD EXTRA GRANDE · 90022050000</t>
+          <t>NUBZ SABOR ROAST BEEF 2 UD JUMBO · 90022040000</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>90022050000</t>
+          <t>90022040000</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -23118,16 +23118,16 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>NUBZ SABOR ROAST BEEF 2 UD JUMBO · 90022040000</t>
+          <t>NY SNACK DENTAL 1CT · 93500000332</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>90022040000</t>
+          <t>93500000332</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -23138,16 +23138,16 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL 1CT · 93500000332</t>
+          <t>NY SNACK DENTAL FILET MIGNON 160U · 93504590000</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>93500000332</t>
+          <t>93504590000</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -23158,16 +23158,16 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON 160U · 93504590000</t>
+          <t>NY SNACK DENTAL FILET MIGNON LG 20U · 93513760000</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>93504590000</t>
+          <t>93513760000</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -23178,16 +23178,16 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON LG 20U · 93513760000</t>
+          <t>NY SNACK DENTAL FILET MIGNON MED40U · 93504940000</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>93513760000</t>
+          <t>93504940000</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -23198,16 +23198,16 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON MED40U · 93504940000</t>
+          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>93504940000</t>
+          <t>93504600000</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -23218,16 +23218,16 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
+          <t>NY SNACK RELLENO 12CT · 93500000336</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>93504600000</t>
+          <t>93500000336</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -23238,16 +23238,16 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>NY SNACK RELLENO 12CT · 93500000336</t>
+          <t>NY SNACK RELLENO 2CT · 93500000337</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>93500000336</t>
+          <t>93500000337</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -23258,16 +23258,16 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>NY SNACK RELLENO 2CT · 93500000337</t>
+          <t>NY SNACKS MINI PARA PERROS 160U · 93504410000</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>93500000337</t>
+          <t>93504410000</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -23278,16 +23278,16 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>NY SNACKS MINI PARA PERROS 160U · 93504410000</t>
+          <t>NY SNACKS MINI PARA PERROS 32U · 93504080000</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>93504410000</t>
+          <t>93504080000</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -23298,16 +23298,16 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>NY SNACKS MINI PARA PERROS 32U · 93504080000</t>
+          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>93504080000</t>
+          <t>93507970000</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -23318,16 +23318,16 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
+          <t>NYLABONE HUESO MD SABOR BISONTE · 93507930000</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>93507970000</t>
+          <t>93507930000</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -23338,12 +23338,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO MD SABOR BISONTE · 93507930000</t>
+          <t>NYLABONE HUESO P/CACHOR CORDERO/MAN · 93508360000</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>93507930000</t>
+          <t>93508360000</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -23358,16 +23358,16 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO P/CACHOR CORDERO/MAN · 93508360000</t>
+          <t>NYLABONE HUESO P/CACHOR PATATA PAVO · 93508330000</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>93508360000</t>
+          <t>93508330000</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -23378,16 +23378,16 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO P/CACHOR PATATA PAVO · 93508330000</t>
+          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>93508330000</t>
+          <t>93508280000</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -23398,16 +23398,16 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
+          <t>NYLABONE HUESO PETITE SABOR TOCINO · 93508190000</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>93508280000</t>
+          <t>93508190000</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -23418,16 +23418,16 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE SABOR TOCINO · 93508190000</t>
+          <t>NYLABONE HUESO REG PATATA PAVO · 93508340000</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>93508190000</t>
+          <t>93508340000</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -23438,16 +23438,16 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO REG PATATA PAVO · 93508340000</t>
+          <t>NYLABONE HUESO REGULAR SABOR TOCINO · 93508200000</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>93508340000</t>
+          <t>93508200000</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -23458,16 +23458,16 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO REGULAR SABOR TOCINO · 93508200000</t>
+          <t>NYLABONE HUESO SUPER CARNE ASADA · 93508320000</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>93508200000</t>
+          <t>93508320000</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -23478,16 +23478,16 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER CARNE ASADA · 93508320000</t>
+          <t>NYLABONE HUESO SUPER SABOR POLLO · 93508270000</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>93508320000</t>
+          <t>93508270000</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -23498,16 +23498,16 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER SABOR POLLO · 93508270000</t>
+          <t>NYLABONE HUESO SUPER SABOR TOCINO · 93508230000</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>93508270000</t>
+          <t>93508230000</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -23518,16 +23518,16 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO SUPER SABOR TOCINO · 93508230000</t>
+          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>93508230000</t>
+          <t>93508370000</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -23538,16 +23538,16 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
+          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>93508370000</t>
+          <t>93508300000</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -23558,12 +23558,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
+          <t>NYLABONE HUESO WOLF SABOR POLLO · 93508250000</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>93508300000</t>
+          <t>93508250000</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -23578,36 +23578,36 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO WOLF SABOR POLLO · 93508250000</t>
+          <t>OLA CANARIOS 800GRS · 90405520000</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>93508250000</t>
+          <t>90405520000</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>OLA CANARIOS 800GRS · 90405520000</t>
+          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>90405520000</t>
+          <t>90405540000</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -23618,36 +23618,36 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
+          <t>PEDIGREE ADULTO 2KG · 90300120000</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>90405540000</t>
+          <t>90300120000</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>PEDIGREE ADULTO 2KG · 90300120000</t>
+          <t>PEDIGREE ADULTO ETG 1KG · 90028420000</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>90300120000</t>
+          <t>90028420000</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -23658,16 +23658,16 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>PEDIGREE ADULTO ETG 1KG · 90028420000</t>
+          <t>PEDIGREE CACHORRO 2KG · 90300140000</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>90028420000</t>
+          <t>90300140000</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -23678,16 +23678,16 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>PEDIGREE CACHORRO 2KG · 90300140000</t>
+          <t>PEDIGREE CACHORRO NUTRIDEFENSE 1KG · 90028410000</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>90300140000</t>
+          <t>90028410000</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -23698,16 +23698,16 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>PEDIGREE CACHORRO NUTRIDEFENSE 1KG · 90028410000</t>
+          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>90028410000</t>
+          <t>90413790000</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -23718,16 +23718,16 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
+          <t>PEDIGREE LATA CACHORRO 375GR · 90408540000</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>90413790000</t>
+          <t>90408540000</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -23738,16 +23738,16 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CACHORRO 375GR · 90408540000</t>
+          <t>PEDIGREE LATA CHOPPED BEEF 375GR · 90408530000</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>90408540000</t>
+          <t>90408530000</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -23758,16 +23758,16 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CHOPPED BEEF 375GR · 90408530000</t>
+          <t>PEDIGREE LATA CHOPPED CHICKEN 375GR · 90408560000</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>90408530000</t>
+          <t>90408560000</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -23778,12 +23778,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA CHOPPED CHICKEN 375GR · 90408560000</t>
+          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>90408560000</t>
+          <t>93509400000</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -23798,16 +23798,16 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
+          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>93509400000</t>
+          <t>93509410000</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -23818,16 +23818,16 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
+          <t>PEDIGREE POUCH RES ADULTO 100GR · 93509420000</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>93509410000</t>
+          <t>93509420000</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -23838,16 +23838,16 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>PEDIGREE POUCH RES ADULTO 100GR · 93509420000</t>
+          <t>PEDIGREE RAZA PEQ POUCH RES 100GR · 93512290000</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>93509420000</t>
+          <t>93512290000</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -23858,16 +23858,16 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZA PEQ POUCH RES 100GR · 93512290000</t>
+          <t>PEDIGREE RAZAS PEQUENAS 2KG · 90407740000</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>93512290000</t>
+          <t>90407740000</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -23878,56 +23878,56 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>PEDIGREE RAZAS PEQUENAS 2KG · 90407740000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>90407740000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>D PF CARE CHEWZ ENROLLADO/COLAGENO 2U · 93517870000</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>93517870000</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ ENROLLADO/COLAGENO 2U · 93517870000</t>
+          <t>D PF CARE CHEWZ TWIST/COLAGENO 2UD · 93517830000</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>93517870000</t>
+          <t>93517830000</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -23938,16 +23938,16 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ TWIST/COLAGENO 2UD · 93517830000</t>
+          <t>D PF CARE CHEWZ WRAP/COLAGENO POLLO · 93517860000</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>93517830000</t>
+          <t>93517860000</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -23958,16 +23958,16 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>D PF CARE CHEWZ WRAP/COLAGENO POLLO · 93517860000</t>
+          <t>D PF CARNAZA ENROLLADA SABOR MANZANA · 93518230000</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>93517860000</t>
+          <t>93518230000</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -23978,12 +23978,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>D PF CARNAZA ENROLLADA SABOR MANZANA · 93518230000</t>
+          <t>D PF HUESO/ CARNAZA SABOR NATUR 11-12 · 93514350000</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>93518230000</t>
+          <t>93514350000</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -23998,16 +23998,16 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>D PF HUESO/ CARNAZA SABOR NATUR 11-12 · 93514350000</t>
+          <t>D PF LAZO DE CARNAZA SABOR MANZANA 2U · 93518240000</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>93514350000</t>
+          <t>93518240000</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -24018,16 +24018,16 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>D PF LAZO DE CARNAZA SABOR MANZANA 2U · 93518240000</t>
+          <t>D PF LAZO DE CARNAZA SABOR MENTA 2UD · 93518220000</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>93518240000</t>
+          <t>93518220000</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -24038,16 +24038,16 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>D PF LAZO DE CARNAZA SABOR MENTA 2UD · 93518220000</t>
+          <t>D PF ROLLO/ CARNAZA SABOR CARNE 10IN · 93514190000</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>93518220000</t>
+          <t>93514190000</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -24058,16 +24058,16 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>D PF ROLLO/ CARNAZA SABOR CARNE 10IN · 93514190000</t>
+          <t>D PF ROLLO/ CARNAZA SABOR M.MANI 8IN · 93514300000</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>93514190000</t>
+          <t>93514300000</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -24078,16 +24078,16 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>D PF ROLLO/ CARNAZA SABOR M.MANI 8IN · 93514300000</t>
+          <t>PF CARE CHEWZ ENROLLADO/COLAGENO 4U · 93517850000</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>93514300000</t>
+          <t>93517850000</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -24098,12 +24098,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ ENROLLADO/COLAGENO 4U · 93517850000</t>
+          <t>PF CARE CHEWZ TWIST/COLAGENO POLLO · 93517820000</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>93517850000</t>
+          <t>93517820000</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -24118,16 +24118,16 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>PF CARE CHEWZ TWIST/COLAGENO POLLO · 93517820000</t>
+          <t>PF CARECHEWZ COLAGENO ENROLL POLLO · 93517800000</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>93517820000</t>
+          <t>93517800000</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -24138,16 +24138,16 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>PF CARECHEWZ COLAGENO ENROLL POLLO · 93517800000</t>
+          <t>PF HUESO/ CARNAZA SABOR CARNE 6-7IN · 93514170000</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>93517800000</t>
+          <t>93514170000</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -24158,16 +24158,16 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR CARNE 6-7IN · 93514170000</t>
+          <t>PF HUESO/ CARNAZA SABOR CARNE 8-9IN · 93514180000</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>93514170000</t>
+          <t>93514180000</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -24178,16 +24178,16 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR CARNE 8-9IN · 93514180000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 6-7IN · 93514270000</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>93514180000</t>
+          <t>93514270000</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -24198,16 +24198,16 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 6-7IN · 93514270000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>93514270000</t>
+          <t>93514280000</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -24218,16 +24218,16 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATU 15-17 · 93514370000</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>93514280000</t>
+          <t>93514370000</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -24238,16 +24238,16 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATU 15-17 · 93514370000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATURA 7-8IN · 93514330000</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>93514370000</t>
+          <t>93514330000</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -24258,16 +24258,16 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATURA 7-8IN · 93514330000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 6-7IN · 93514220000</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>93514330000</t>
+          <t>93514220000</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -24278,16 +24278,16 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 6-7IN · 93514220000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>93514220000</t>
+          <t>93514230000</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -24298,16 +24298,16 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>PF ROLLO/ CARNAZA SABOR CARNE 8IN · 93514200000</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>93514230000</t>
+          <t>93514200000</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -24318,16 +24318,16 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR CARNE 8IN · 93514200000</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>93514200000</t>
+          <t>93514240000</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -24338,16 +24338,16 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 8IN · 93514250000</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>93514240000</t>
+          <t>93514250000</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -24358,16 +24358,16 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 8IN · 93514250000</t>
+          <t>PF ROLLO/CARNAZA SABOR NATURAL 10IN · 93517740000</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>93514250000</t>
+          <t>93517740000</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>PF ROLLO/CARNAZA SABOR NATURAL 10IN · 93517740000</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 12IN · 93517770000</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>93517740000</t>
+          <t>93517770000</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -24398,16 +24398,16 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 12IN · 93517770000</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>93517770000</t>
+          <t>93517760000</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -24418,36 +24418,36 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
+          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>93517760000</t>
+          <t>90411220000</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
+          <t>SD CANINE C/D 8.5LB · 90304040000</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>90411220000</t>
+          <t>90304040000</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -24458,16 +24458,16 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SD CANINE C/D 8.5LB · 90304040000</t>
+          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>90304040000</t>
+          <t>90304010000</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -24478,16 +24478,16 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
+          <t>SD CANINE K/D 17.5LBS · 90411470000</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>90304010000</t>
+          <t>90411470000</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -24498,16 +24498,16 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>SD CANINE K/D 17.5LBS · 90411470000</t>
+          <t>SD CANINE K/D 8.5LB · 90303990000</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>90411470000</t>
+          <t>90303990000</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -24518,16 +24518,16 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>SD CANINE K/D 8.5LB · 90303990000</t>
+          <t>SD CANINE U/D DRY 8.5LB · 90304020000</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>90303990000</t>
+          <t>90304020000</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -24538,16 +24538,16 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>SD CANINE U/D DRY 8.5LB · 90304020000</t>
+          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>90304020000</t>
+          <t>90304470000</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -24558,16 +24558,16 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
+          <t>SD FELINE K/D 4 LB · 90402960000</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>90304470000</t>
+          <t>90402960000</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -24578,12 +24578,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>SD FELINE K/D 4 LB · 90402960000</t>
+          <t>SD HILLS CANINE J/D 8.5LB · 90404660000</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>90402960000</t>
+          <t>90404660000</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -24598,16 +24598,16 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>SD HILLS CANINE J/D 8.5LB · 90404660000</t>
+          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>90404660000</t>
+          <t>90406520000</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -24618,16 +24618,16 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
+          <t>SD LATA CANINE K/D12/ 13 OZ. · 90406540000</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>90406520000</t>
+          <t>90406540000</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -24638,16 +24638,16 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>SD LATA CANINE K/D12/ 13 OZ. · 90406540000</t>
+          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>90406540000</t>
+          <t>90406480000</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -24658,16 +24658,16 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
+          <t>SD LATA CANINE W/D12/13OZ · 90406510000</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>90406480000</t>
+          <t>90406510000</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -24678,16 +24678,16 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>SD LATA CANINE W/D12/13OZ · 90406510000</t>
+          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>90406510000</t>
+          <t>90409360000</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -24698,16 +24698,16 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
+          <t>SD PD CANIN H/D 3.3LB · 93516950000</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>90409360000</t>
+          <t>93516950000</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -24718,16 +24718,16 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>SD PD CANIN H/D 3.3LB · 93516950000</t>
+          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>93516950000</t>
+          <t>93517020000</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -24738,16 +24738,16 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
+          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>93517020000</t>
+          <t>93516960000</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -24758,16 +24758,16 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
+          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>93516960000</t>
+          <t>93516970000</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -24778,16 +24778,16 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>SD PD CANINE METABOLISMO 7LB · 93517000000</t>
+          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>93517000000</t>
+          <t>93516980000</t>
         </is>
       </c>
       <c r="C570" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -24798,16 +24798,16 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
+          <t>SD PD GATO I/D 4LB · 93517090000</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>93516970000</t>
+          <t>93517090000</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -24818,16 +24818,16 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
+          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>93516980000</t>
+          <t>93517100000</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -24838,16 +24838,16 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D 4LB · 93517090000</t>
+          <t>SD PD GATOS W/D 4LB · 93517050000</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>93517090000</t>
+          <t>93517050000</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -24858,16 +24858,16 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>93517100000</t>
+          <t>93517060000</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -24878,56 +24878,56 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>SD PD GATOS W/D 4LB · 93517050000</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>93517050000</t>
+          <t>93500000100</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>93517060000</t>
+          <t>93500000200</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PRO PET 10KG ADULTO · 93500000500</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>93500000100</t>
+          <t>93500000500</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -24938,16 +24938,16 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PRO PET 18KG ADULTO · 93500000600</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>93500000200</t>
+          <t>93500000600</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -24958,16 +24958,16 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>PRO PET 10KG ADULTO · 93500000500</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>93500000500</t>
+          <t>93500000300</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -24978,16 +24978,16 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>PRO PET 18KG ADULTO · 93500000600</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>93500000600</t>
+          <t>93500000400</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -24998,56 +24998,56 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>93500000300</t>
+          <t>90009660000</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>93500000400</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
+          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>90009660000</t>
+          <t>93501251000</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -25058,16 +25058,16 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>93510171000</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -25078,12 +25078,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>PP ADULTO RZ PEQUENA OPTI 7.5KG · 93501251000</t>
+          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>93501251000</t>
+          <t>93510181000</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -25098,12 +25098,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>93510171000</t>
+          <t>93501121000</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -25118,16 +25118,16 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  MD/G 13KG · 93510181000</t>
+          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>93510181000</t>
+          <t>90403691000</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -25138,16 +25138,16 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>PP CACHORRO RZ GRANDE 3.5KG · 93501121000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>93501121000</t>
+          <t>93519420000</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -25158,16 +25158,16 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>PP GATO ADULTO SALMON 85G · 90403691000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>90403691000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -25178,16 +25178,16 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>93519420000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -25198,16 +25198,16 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -25218,16 +25218,16 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -25238,12 +25238,12 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -25258,16 +25258,16 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -25278,16 +25278,16 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -25298,16 +25298,16 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -25318,16 +25318,16 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -25338,16 +25338,16 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -25358,16 +25358,16 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -25378,16 +25378,16 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -25398,16 +25398,16 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519520000</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -25418,16 +25418,16 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93519480000</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -25438,16 +25438,16 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>93519520000</t>
+          <t>93520280000</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -25458,16 +25458,16 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>93519480000</t>
+          <t>93520220000</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -25478,16 +25478,16 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
+          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>93520280000</t>
+          <t>93520140000</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -25498,12 +25498,12 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO RZ MD 13KG · 93520220000</t>
+          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>93520220000</t>
+          <t>93520240000</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -25518,16 +25518,16 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO SENSIBLE MD 3KG · 93520140000</t>
+          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>93520140000</t>
+          <t>93520210000</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -25538,16 +25538,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>PP PROPLAN BAJO EN CALORIAS 3KG · 93520240000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>93520240000</t>
+          <t>93520200000</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -25558,16 +25558,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ GDE 13KG · 93520210000</t>
+          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>93520210000</t>
+          <t>93520190000</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -25578,16 +25578,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 13KG · 93520200000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>93520200000</t>
+          <t>93520160000</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -25598,12 +25598,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ MD 7.5KG · 93520190000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>93520190000</t>
+          <t>93520180000</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -25618,16 +25618,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
+          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>93520160000</t>
+          <t>93520260000</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -25638,16 +25638,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 7.5KG · 93520180000</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>93520180000</t>
+          <t>93520130000</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -25658,16 +25658,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS POUCH 85 G · 93520260000</t>
+          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>93520260000</t>
+          <t>93520250000</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -25678,16 +25678,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
+          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>93520130000</t>
+          <t>93520230000</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -25698,16 +25698,16 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>PP PROPLAN GATITO POLLO/ARROZ 1.5KG · 93520250000</t>
+          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>93520250000</t>
+          <t>93520150000</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -25718,16 +25718,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>PP PROPLAN MENTE ACTIVA RZ MD 3KG · 93520230000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>93520230000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -25738,16 +25738,16 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>PP PROPLAN RZ MD Y GDE OPTIFIT 13KG · 93520150000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>93520150000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -25758,16 +25758,16 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038590000</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -25798,16 +25798,16 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>93520060000</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -25818,16 +25818,16 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
+          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>90038590000</t>
+          <t>93520070000</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -25838,16 +25838,16 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO EXIGENTE RZ PQNA 3KG · 93520060000</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>93520060000</t>
+          <t>93520000000</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -25858,16 +25858,16 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MD OPTIHEALTH 7.5 · 93520070000</t>
+          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>93520070000</t>
+          <t>90038580000</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -25878,16 +25878,16 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>93520000000</t>
+          <t>93519980000</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -25898,12 +25898,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>PROPLAN EXIGENT BOCADOS PEQUENOS 1KG MX · 90038580000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>90038580000</t>
+          <t>93519990000</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -25918,12 +25918,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
+          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>93519980000</t>
+          <t>90038610000</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -25938,12 +25938,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>93519990000</t>
+          <t>93520010000</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -25958,16 +25958,16 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>PROPLAN MENTE ACTIVA BOCADOS PEQ 1KG MX · 90038610000</t>
+          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>90038610000</t>
+          <t>90038600000</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -25978,16 +25978,16 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>PROPLAN OPTIDERMA RZ PQNA 7.5KG · 93520010000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>93520010000</t>
+          <t>90038570000</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -25998,56 +25998,56 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>PROPLAN PIEL SENSI ADULTO RAZAS PEQ 1KG · 90038600000</t>
+          <t>D PC MEZCLA P/PASTEL SABOR BANANA · 93518830000</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>90038600000</t>
+          <t>93518830000</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PUPPY CAKE</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PC KIT P/PASTEL CUMPLEANOS CALABAZA · 93518920000</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>90038570000</t>
+          <t>93518920000</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PUPPY CAKE</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>D PC MEZCLA P/PASTEL SABOR BANANA · 93518830000</t>
+          <t>PC KIT P/PASTEL D CUMPLEANOS M MANNÂ · 93518900000</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>93518830000</t>
+          <t>93518900000</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -26058,12 +26058,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>PC KIT P/PASTEL CUMPLEANOS CALABAZA · 93518920000</t>
+          <t>PC KIT PARA PASTEL DE CUMPLEANOS · 93518860000</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>93518920000</t>
+          <t>93518860000</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -26078,16 +26078,16 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>PC KIT P/PASTEL D CUMPLEANOS M MANNÂ · 93518900000</t>
+          <t>PC KIT PASTEL DE CUMPLEANOS/BANANA · 93518840000</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>93518900000</t>
+          <t>93518840000</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -26098,16 +26098,16 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>PC KIT PARA PASTEL DE CUMPLEANOS · 93518860000</t>
+          <t>PC MEZCLA P/PASTEL CUMPLEANOS CALAB · 93518910000</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>93518860000</t>
+          <t>93518910000</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -26118,16 +26118,16 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>PC KIT PASTEL DE CUMPLEANOS/BANANA · 93518840000</t>
+          <t>PC MEZCLA P/PASTEL CUMPLEANOS MMANN? · 93518890000</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>93518840000</t>
+          <t>93518890000</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -26138,16 +26138,16 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>PC MEZCLA P/PASTEL CUMPLEANOS CALAB · 93518910000</t>
+          <t>PC MEZCLA PARA PASTEL DE CUMPLEANOS · 93518850000</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>93518910000</t>
+          <t>93518850000</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -26158,56 +26158,56 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>PC MEZCLA P/PASTEL CUMPLEANOS MMANN? · 93518890000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>93518890000</t>
+          <t>90040920000</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>PUPPY CAKE</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>PC MEZCLA PARA PASTEL DE CUMPLEANOS · 93518850000</t>
+          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>93518850000</t>
+          <t>90040930000</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>PUPPY CAKE</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>90040920000</t>
+          <t>93520020000</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -26218,16 +26218,16 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
+          <t>PRO PLAN ADULTO RAZA PEQUEÑA 4x3.5kgMX · 90026960000</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>90040930000</t>
+          <t>90026960000</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -26238,16 +26238,16 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
+          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>93520020000</t>
+          <t>90026950000</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -26258,16 +26258,16 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>PRO PLAN ADULTO RAZA PEQUEÑA 4x3.5kgMX · 90026960000</t>
+          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>90026960000</t>
+          <t>93516230000</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -26278,16 +26278,16 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
+          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>90026950000</t>
+          <t>93516200000</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -26298,16 +26298,16 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>93516230000</t>
+          <t>93516210000</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -26318,56 +26318,56 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
+          <t>D RB  HUESO PQNO RELLENO M MANNÂ · 93512200000</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>93516200000</t>
+          <t>93512200000</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>D RB CUERNO DE RES RELLENO DE CARNE · 93512120000</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>93516210000</t>
+          <t>93512120000</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>D RB  HUESO PQNO RELLENO M MANNÂ · 93512200000</t>
+          <t>D RB HUESO LARGO RELLENO D CARNE · 93512150000</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>93512200000</t>
+          <t>93512150000</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -26378,12 +26378,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>D RB CUERNO DE RES RELLENO DE CARNE · 93512120000</t>
+          <t>D RB HUESO LARGO RELLENO D POLLO · 93512170000</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>93512120000</t>
+          <t>93512170000</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -26398,16 +26398,16 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO D CARNE · 93512150000</t>
+          <t>D RB HUESO LARGO RELLENO M MANI · 93512190000</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>93512150000</t>
+          <t>93512190000</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -26418,16 +26418,16 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO D POLLO · 93512170000</t>
+          <t>D RB HUESO LARGO RELLENO QUESO/TOCINO · 93512130000</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>93512170000</t>
+          <t>93512130000</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -26438,16 +26438,16 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO M MANI · 93512190000</t>
+          <t>D RB HUESO PQNO RELLENO DE CARNE · 93512160000</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>93512190000</t>
+          <t>93512160000</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -26458,16 +26458,16 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>D RB HUESO LARGO RELLENO QUESO/TOCINO · 93512130000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>93512130000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -26478,16 +26478,16 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE CARNE · 93512160000</t>
+          <t>D RB HUESO PQNO RELLENO QUESO/TOCINO · 93512140000</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>93512160000</t>
+          <t>93512140000</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -26498,56 +26498,56 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>BHN CHIHUAHUA PUPPY 1.5KG · 90413690000</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>90413690000</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO QUESO/TOCINO · 93512140000</t>
+          <t>FCN URINARY CARE 2KG · 90413901000</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>93512140000</t>
+          <t>90413901000</t>
         </is>
       </c>
       <c r="C657" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>BHN CHIHUAHUA PUPPY 1.5KG · 90413690000</t>
+          <t>FHN BABY CAT 400GR · 90413910100</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>90413690000</t>
+          <t>90413910100</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -26558,12 +26558,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>FCN URINARY CARE 2KG · 90413901000</t>
+          <t>FHN HAIRBALL CARE 400GR · 90413930100</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>90413901000</t>
+          <t>90413930100</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -26578,16 +26578,16 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>FHN BABY CAT 400GR · 90413910100</t>
+          <t>FHN STERILISED 2KG · 90414280000</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>90413910100</t>
+          <t>90414280000</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -26598,16 +26598,16 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>FHN HAIRBALL CARE 400GR · 90413930100</t>
+          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>90413930100</t>
+          <t>90401980000</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -26618,16 +26618,16 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>FHN STERILISED 2KG · 90414280000</t>
+          <t>ROYAL CANI ADULTO YORKSHIRE 1.5 KG. · 90401970000</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>90414280000</t>
+          <t>90401970000</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -26638,16 +26638,16 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
+          <t>ROYAL CANIN  FELINE FIT32-2 KG · 90401390000</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>90401980000</t>
+          <t>90401390000</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -26658,12 +26658,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>ROYAL CANI ADULTO YORKSHIRE 1.5 KG. · 90401970000</t>
+          <t>ROYAL CANIN  MAXI PUPPY 4 KG. · 90401720000</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>90401970000</t>
+          <t>90401720000</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -26678,16 +26678,16 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>ROYAL CANIN  FELINE FIT32-2 KG · 90401390000</t>
+          <t>ROYAL CANIN ADULT POODLE 1.5KG · 90401950000</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>90401390000</t>
+          <t>90401950000</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -26698,16 +26698,16 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>ROYAL CANIN  MAXI PUPPY 4 KG. · 90401720000</t>
+          <t>ROYAL CANIN ALIM. BABY CAT 2 KG · 90404370000</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>90401720000</t>
+          <t>90404370000</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -26718,16 +26718,16 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ADULT POODLE 1.5KG · 90401950000</t>
+          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>90401950000</t>
+          <t>90401430000</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -26738,16 +26738,16 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. BABY CAT 2 KG · 90404370000</t>
+          <t>ROYAL CANIN ALIM. P GATITOS 400GR · 90404300000</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>90404370000</t>
+          <t>90404300000</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -26758,16 +26758,16 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
+          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>90401430000</t>
+          <t>90412110000</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -26778,16 +26778,16 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. P GATITOS 400GR · 90404300000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>90404300000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -26798,16 +26798,16 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
+          <t>ROYAL CANIN GATO PERSA 2KG · 90410060000</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>90412110000</t>
+          <t>90410060000</t>
         </is>
       </c>
       <c r="C671" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -26818,16 +26818,16 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -26838,16 +26838,16 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO PERSA 2KG · 90410060000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>90410060000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -26858,16 +26858,16 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN HEPATIC 7KG · 90021670000</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>90021670000</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -26878,16 +26878,16 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -26898,12 +26898,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 7KG · 90021670000</t>
+          <t>ROYAL CANIN INDOOR 27 2 KG · 90404330000</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>90021670000</t>
+          <t>90404330000</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -26918,12 +26918,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN MAXI ADULTO 15KG. · 90401790000</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>90401790000</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -26938,16 +26938,16 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>ROYAL CANIN INDOOR 27 2 KG · 90404330000</t>
+          <t>ROYAL CANIN MAXI ADULTO 4 KG · 90401750000</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>90404330000</t>
+          <t>90401750000</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -26958,16 +26958,16 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI ADULTO 15KG. · 90401790000</t>
+          <t>ROYAL CANIN MEDIUM ADULTO 10 KG · 90401590000</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>90401790000</t>
+          <t>90401590000</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -26978,16 +26978,16 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MAXI ADULTO 4 KG · 90401750000</t>
+          <t>ROYAL CANIN MEDIUM ADULTO 4KG · 90401570000</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>90401750000</t>
+          <t>90401570000</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -26998,12 +26998,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM ADULTO 10 KG · 90401590000</t>
+          <t>ROYAL CANIN MEDIUM PUPPY 4 KG · 90401540000</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>90401590000</t>
+          <t>90401540000</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -27018,16 +27018,16 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM ADULTO 4KG · 90401570000</t>
+          <t>ROYAL CANIN MINI ADULT 8+ 2KG · 90401530000</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>90401570000</t>
+          <t>90401530000</t>
         </is>
       </c>
       <c r="C682" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -27038,16 +27038,16 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM PUPPY 4 KG · 90401540000</t>
+          <t>ROYAL CANIN MINI ADULTO 2 KG. · 90401490000</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>90401540000</t>
+          <t>90401490000</t>
         </is>
       </c>
       <c r="C683" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -27058,16 +27058,16 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULT 8+ 2KG · 90401530000</t>
+          <t>ROYAL CANIN MINI ADULTO 800GR · 90006740000</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>90401530000</t>
+          <t>90006740000</t>
         </is>
       </c>
       <c r="C684" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -27078,16 +27078,16 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULTO 2 KG. · 90401490000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>90401490000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C685" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -27098,16 +27098,16 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MINI ADULTO 800GR · 90006740000</t>
+          <t>ROYAL CANIN SHN MINI ADULT 8K · 90403640000</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>90006740000</t>
+          <t>90403640000</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -27118,16 +27118,16 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN SHN MINI ADULTO 4KG · 90409890000</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>90409890000</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -27138,16 +27138,16 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI ADULT 8K · 90403640000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>90403640000</t>
+          <t>90404120000</t>
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -27158,16 +27158,16 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI ADULTO 4KG · 90409890000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 4K · 90404060000</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>90409890000</t>
+          <t>90404060000</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -27178,16 +27178,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>90404120000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -27198,12 +27198,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 4K · 90404060000</t>
+          <t>ROYAL CANIN XSMALL ADULTO 1.5 KG · 90006750000</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>90404060000</t>
+          <t>90006750000</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -27218,16 +27218,16 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYAL CANIN XSMALL PUPPY 1.5KG · 90006760000</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>90006760000</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -27238,16 +27238,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>ROYAL CANIN XSMALL ADULTO 1.5 KG · 90006750000</t>
+          <t>SHN MINI PUPPY 800GR · 90414290000</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>90006750000</t>
+          <t>90414290000</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -27258,16 +27258,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>ROYAL CANIN XSMALL PUPPY 1.5KG · 90006760000</t>
+          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>90006760000</t>
+          <t>90414301000</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -27278,56 +27278,56 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>SHN MINI PUPPY 800GR · 90414290000</t>
+          <t>D UC SNACK BARRA RELLENA YOGURT 8UD · 93514970000</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>90414290000</t>
+          <t>93514970000</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
+          <t>UC SNACK BARRA RELLENA DE HIGADO 1 · 93513070000</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>90414301000</t>
+          <t>93513070000</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>D UC SNACK BARRA RELLENA YOGURT 8UD · 93514970000</t>
+          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>93514970000</t>
+          <t>93513080000</t>
         </is>
       </c>
       <c r="C697" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -27338,16 +27338,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE HIGADO 1 · 93513070000</t>
+          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>93513070000</t>
+          <t>93513050000</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -27358,16 +27358,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
+          <t>UC SNACK BARRA RELLENA POLLO 8UD · 93514990000</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>93513080000</t>
+          <t>93514990000</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -27378,16 +27378,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
+          <t>UC SNACK V BARRA RELLENA HIGADO 8UD · 93514980000</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>93513050000</t>
+          <t>93514980000</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -27398,16 +27398,16 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA POLLO 8UD · 93514990000</t>
+          <t>UC SNACK V BARRA RELLENA M MANI 8UD · 93514960000</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>93514990000</t>
+          <t>93514960000</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -27418,56 +27418,56 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>UC SNACK V BARRA RELLENA HIGADO 8UD · 93514980000</t>
+          <t>D SIMPLY NAKED ALIM P/PERRO MARISCOS 4LB · 93500000399</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>93514980000</t>
+          <t>93500000399</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SIMPLY NAKED</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>UC SNACK V BARRA RELLENA M MANI 8UD · 93514960000</t>
+          <t>D SIMPLY NAKED ALIM/GATO PESCADO 4LB · 93500000404</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>93514960000</t>
+          <t>93500000404</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SIMPLY NAKED</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>D SIMPLY NAKED ALIM P/PERRO MARISCOS 4LB · 93500000399</t>
+          <t>D SIMPLY NAKED ALIM/GATO SALMON 4LB · 93500000402</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>93500000399</t>
+          <t>93500000402</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -27478,16 +27478,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>D SIMPLY NAKED ALIM/GATO PESCADO 4LB · 93500000404</t>
+          <t>DSIMPLY NAKED ALIM/GATO PESCADO ROJO 4LB · 93500000406</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>93500000404</t>
+          <t>93500000406</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -27498,76 +27498,76 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>D SIMPLY NAKED ALIM/GATO SALMON 4LB · 93500000402</t>
+          <t>D SMARTBONE POLLO SMALL 3UD · 93515680000</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>93500000402</t>
+          <t>93515680000</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>SIMPLY NAKED</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>DSIMPLY NAKED ALIM/GATO PESCADO ROJO 4LB · 93500000406</t>
+          <t>SUPER GATO 1.5KG · 93500000800</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>93500000406</t>
+          <t>93500000800</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>SIMPLY NAKED</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>D SMARTBONE POLLO SMALL 3UD · 93515680000</t>
+          <t>SUPER GATO 500GRS · 93500000700</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>93515680000</t>
+          <t>93500000700</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>SUPER GATO 1.5KG · 93500000800</t>
+          <t>SUPER GATO 8KG · 93500000900</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>93500000800</t>
+          <t>93500000900</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -27578,56 +27578,56 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>SUPER GATO 500GRS · 93500000700</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>93500000700</t>
+          <t>93511630000</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>SUPER GATO 8KG · 93500000900</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>93500000900</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>93511630000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -27638,16 +27638,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 4KG · 93500000343</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000343</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -27658,16 +27658,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -27678,16 +27678,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 4KG · 93500000343</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>93500000343</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -27698,56 +27698,56 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>D SUPRA ADULTO 10KG · 93508880000</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93508880000</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>D SUPRA ADULTO 10KG · 93508880000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>93508880000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -27758,16 +27758,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -27778,16 +27778,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -27798,16 +27798,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -27818,16 +27818,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -27838,16 +27838,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 18KG · 93508940000</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508940000</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -27858,16 +27858,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>93508950000</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -27878,12 +27878,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 18KG · 93508940000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>93508940000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -27898,72 +27898,72 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>93508950000</t>
+          <t>90334000000</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90013320000</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TASTE OF THE WILD</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>90334000000</t>
+          <t>90013340000</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TASTE OF THE WILD</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>90013320000</t>
+          <t>90013260000</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -27978,16 +27978,16 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
+          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>90013340000</t>
+          <t>90013210000</t>
         </is>
       </c>
       <c r="C730" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -27998,16 +27998,16 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
+          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>90013260000</t>
+          <t>90013380000</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -28018,16 +28018,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
+          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>90013210000</t>
+          <t>90013280000</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -28038,16 +28038,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
+          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>90013380000</t>
+          <t>90013170000</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -28058,16 +28058,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
+          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>90013280000</t>
+          <t>90013390000</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -28078,16 +28078,16 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
+          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>90013170000</t>
+          <t>90013270000</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -28098,16 +28098,16 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
+          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>90013390000</t>
+          <t>90013410000</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -28118,16 +28118,16 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
+          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>90013270000</t>
+          <t>90013370000</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -28138,16 +28138,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
+          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>90013410000</t>
+          <t>90013300000</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -28158,16 +28158,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
+          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>90013370000</t>
+          <t>90013230000</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -28178,16 +28178,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
+          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>90013300000</t>
+          <t>90013180000</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -28198,16 +28198,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
+          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>90013230000</t>
+          <t>90013250000</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -28218,16 +28218,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>90013180000</t>
+          <t>90013350000</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -28238,16 +28238,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
+          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>90013250000</t>
+          <t>90013190000</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -28258,16 +28258,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>90013350000</t>
+          <t>90013400000</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -28278,16 +28278,16 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>90013400000</t>
+          <t>90013290000</t>
         </is>
       </c>
       <c r="C745" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>
